--- a/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44439</v>
       </c>
       <c r="B2" t="n">
-        <v>0.631159</v>
+        <v>0.79016</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44469</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.055529</v>
+        <v>-0.119484</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44500</v>
       </c>
       <c r="B4" t="n">
-        <v>0.53429</v>
+        <v>0.53809</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44530</v>
       </c>
       <c r="B5" t="n">
-        <v>1.599501</v>
+        <v>1.529727</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44561</v>
       </c>
       <c r="B6" t="n">
-        <v>0.250195</v>
+        <v>0.384723</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44592</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.889415</v>
+        <v>-2.022457</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44620</v>
       </c>
       <c r="B8" t="n">
-        <v>0.982105</v>
+        <v>1.123069</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44651</v>
       </c>
       <c r="B9" t="n">
-        <v>1.194746</v>
+        <v>1.140381</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44681</v>
       </c>
       <c r="B10" t="n">
-        <v>0.004178</v>
+        <v>-0.043542</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44712</v>
       </c>
       <c r="B11" t="n">
-        <v>0.112442</v>
+        <v>0.158456</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44742</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.156589</v>
+        <v>-0.03998</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44773</v>
       </c>
       <c r="B13" t="n">
-        <v>1.9075</v>
+        <v>1.648569</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44804</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.307887</v>
+        <v>-0.200994</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44834</v>
       </c>
       <c r="B15" t="n">
-        <v>0.051214</v>
+        <v>0.10532</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44865</v>
       </c>
       <c r="B16" t="n">
-        <v>0.283274</v>
+        <v>0.280382</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44895</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.725155</v>
+        <v>-0.789595</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.249038</v>
+        <v>-0.07978200000000001</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>44957</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.342048</v>
+        <v>-0.527112</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>44985</v>
       </c>
       <c r="B20" t="n">
-        <v>2.881581</v>
+        <v>2.956329</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45016</v>
       </c>
       <c r="B21" t="n">
-        <v>0.100866</v>
+        <v>0.08132200000000001</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45046</v>
       </c>
       <c r="B22" t="n">
-        <v>1.051427</v>
+        <v>1.037108</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45077</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.655253</v>
+        <v>-1.726531</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45107</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.06297</v>
+        <v>0.136874</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45138</v>
       </c>
       <c r="B25" t="n">
-        <v>0.458481</v>
+        <v>0.321216</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45169</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.374379</v>
+        <v>-0.370842</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45199</v>
       </c>
       <c r="B27" t="n">
-        <v>0.012734</v>
+        <v>0.123599</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45230</v>
       </c>
       <c r="B28" t="n">
-        <v>0.313403</v>
+        <v>0.290723</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45260</v>
       </c>
       <c r="B29" t="n">
-        <v>0.739043</v>
+        <v>0.632726</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45291</v>
       </c>
       <c r="B30" t="n">
-        <v>1.06955</v>
+        <v>1.324376</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45322</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.194024</v>
+        <v>-0.349526</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45351</v>
       </c>
       <c r="B32" t="n">
-        <v>0.14777</v>
+        <v>0.217311</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45382</v>
       </c>
       <c r="B33" t="n">
-        <v>0.081216</v>
+        <v>-0.047642</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45412</v>
       </c>
       <c r="B34" t="n">
-        <v>0.236126</v>
+        <v>0.045001</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45443</v>
       </c>
       <c r="B35" t="n">
-        <v>0.664278</v>
+        <v>0.907072</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45473</v>
       </c>
       <c r="B36" t="n">
-        <v>0.864098</v>
+        <v>0.822263</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45504</v>
       </c>
       <c r="B37" t="n">
-        <v>0.35244</v>
+        <v>0.29212</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45535</v>
       </c>
       <c r="B38" t="n">
-        <v>0.171599</v>
+        <v>0.239878</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45565</v>
       </c>
       <c r="B39" t="n">
-        <v>0.80633</v>
+        <v>0.7981780000000001</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45596</v>
       </c>
       <c r="B40" t="n">
-        <v>0.192241</v>
+        <v>0.142964</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45626</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.221546</v>
+        <v>-0.155954</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45657</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.76507</v>
+        <v>-0.500274</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45688</v>
       </c>
       <c r="B43" t="n">
-        <v>1.000655</v>
+        <v>0.581806</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45716</v>
       </c>
       <c r="B44" t="n">
-        <v>0.491628</v>
+        <v>0.651126</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45747</v>
       </c>
       <c r="B45" t="n">
-        <v>1.341273</v>
+        <v>1.210865</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45777</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.131764</v>
+        <v>-0.333662</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45808</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.883188</v>
+        <v>-0.658621</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45838</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.208448</v>
+        <v>-0.214439</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45869</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.410362</v>
+        <v>-0.456297</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45900</v>
       </c>
       <c r="B50" t="n">
-        <v>0.393384</v>
+        <v>0.489219</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45930</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.070866</v>
+        <v>-0.150542</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>45961</v>
       </c>
       <c r="B52" t="n">
-        <v>0.02339</v>
+        <v>0.073161</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>45991</v>
       </c>
       <c r="B53" t="n">
-        <v>0.470751</v>
+        <v>0.513402</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46022</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.026441</v>
+        <v>0.131385</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46053</v>
       </c>
       <c r="B55" t="n">
-        <v>0.755789</v>
+        <v>0.582392</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46081</v>
       </c>
       <c r="B56" t="n">
-        <v>0.625412</v>
+        <v>0.548872</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46112</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.180258</v>
+        <v>-0.133871</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,15 @@
         <v>46142</v>
       </c>
       <c r="B58" t="n">
-        <v>0.511964</v>
+        <v>0.404069</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.07079299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,465 +434,457 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B2" t="n">
-        <v>0.79016</v>
+        <v>-0.119484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.119484</v>
+        <v>0.53809</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B4" t="n">
-        <v>0.53809</v>
+        <v>1.529727</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>1.529727</v>
+        <v>0.384723</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B6" t="n">
-        <v>0.384723</v>
+        <v>-2.022457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B7" t="n">
-        <v>-2.022457</v>
+        <v>1.123069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B8" t="n">
-        <v>1.123069</v>
+        <v>1.140381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B9" t="n">
-        <v>1.140381</v>
+        <v>-0.043542</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.043542</v>
+        <v>0.158456</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B11" t="n">
-        <v>0.158456</v>
+        <v>-0.03998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.03998</v>
+        <v>1.648569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B13" t="n">
-        <v>1.648569</v>
+        <v>-0.200994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.200994</v>
+        <v>0.10532</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B15" t="n">
-        <v>0.10532</v>
+        <v>0.280382</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B16" t="n">
-        <v>0.280382</v>
+        <v>-0.789595</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.789595</v>
+        <v>-0.07978200000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.07978200000000001</v>
+        <v>-0.527112</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.527112</v>
+        <v>2.956329</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B20" t="n">
-        <v>2.956329</v>
+        <v>0.08132200000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B21" t="n">
-        <v>0.08132200000000001</v>
+        <v>1.037108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B22" t="n">
-        <v>1.037108</v>
+        <v>-1.726531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.726531</v>
+        <v>0.136874</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B24" t="n">
-        <v>0.136874</v>
+        <v>0.321216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B25" t="n">
-        <v>0.321216</v>
+        <v>-0.370842</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.370842</v>
+        <v>0.123599</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B27" t="n">
-        <v>0.123599</v>
+        <v>0.290723</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B28" t="n">
-        <v>0.290723</v>
+        <v>0.632726</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>0.632726</v>
+        <v>1.324376</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B30" t="n">
-        <v>1.324376</v>
+        <v>-0.349526</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.349526</v>
+        <v>0.217311</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B32" t="n">
-        <v>0.217311</v>
+        <v>-0.047642</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.047642</v>
+        <v>0.045001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B34" t="n">
-        <v>0.045001</v>
+        <v>0.907072</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B35" t="n">
-        <v>0.907072</v>
+        <v>0.822263</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B36" t="n">
-        <v>0.822263</v>
+        <v>0.29212</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B37" t="n">
-        <v>0.29212</v>
+        <v>0.239878</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B38" t="n">
-        <v>0.239878</v>
+        <v>0.7981780000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7981780000000001</v>
+        <v>0.142964</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B40" t="n">
-        <v>0.142964</v>
+        <v>-0.155954</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.155954</v>
+        <v>-0.500274</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.500274</v>
+        <v>0.581806</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B43" t="n">
-        <v>0.581806</v>
+        <v>0.651126</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B44" t="n">
-        <v>0.651126</v>
+        <v>1.210865</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B45" t="n">
-        <v>1.210865</v>
+        <v>-0.333662</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.333662</v>
+        <v>-0.658621</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.658621</v>
+        <v>-0.214439</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.214439</v>
+        <v>-0.456297</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.456297</v>
+        <v>0.489219</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B50" t="n">
-        <v>0.489219</v>
+        <v>-0.150542</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.150542</v>
+        <v>0.073161</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B52" t="n">
-        <v>0.073161</v>
+        <v>0.513402</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B53" t="n">
-        <v>0.513402</v>
+        <v>0.131385</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B54" t="n">
-        <v>0.131385</v>
+        <v>0.582392</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B55" t="n">
-        <v>0.582392</v>
+        <v>0.548872</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B56" t="n">
-        <v>0.548872</v>
+        <v>-0.133871</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.133871</v>
+        <v>0.404069</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B58" t="n">
-        <v>0.404069</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B59" t="n">
         <v>0.07079299999999999</v>
       </c>
     </row>

--- a/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44469</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.119484</v>
+        <v>-0.064886</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44500</v>
       </c>
       <c r="B3" t="n">
-        <v>0.53809</v>
+        <v>0.541272</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44530</v>
       </c>
       <c r="B4" t="n">
-        <v>1.529727</v>
+        <v>1.615792</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>0.384723</v>
+        <v>0.317648</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44592</v>
       </c>
       <c r="B6" t="n">
-        <v>-2.022457</v>
+        <v>-1.96241</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44620</v>
       </c>
       <c r="B7" t="n">
-        <v>1.123069</v>
+        <v>1.093519</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44651</v>
       </c>
       <c r="B8" t="n">
-        <v>1.140381</v>
+        <v>1.076776</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44681</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.043542</v>
+        <v>-0.09649099999999999</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44712</v>
       </c>
       <c r="B10" t="n">
-        <v>0.158456</v>
+        <v>0.206371</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44742</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.03998</v>
+        <v>-0.122134</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44773</v>
       </c>
       <c r="B12" t="n">
-        <v>1.648569</v>
+        <v>1.910705</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44804</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.200994</v>
+        <v>-0.328948</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44834</v>
       </c>
       <c r="B14" t="n">
-        <v>0.10532</v>
+        <v>0.052651</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44865</v>
       </c>
       <c r="B15" t="n">
-        <v>0.280382</v>
+        <v>0.275674</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44895</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.789595</v>
+        <v>-0.709488</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44926</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.07978200000000001</v>
+        <v>-0.124753</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44957</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.527112</v>
+        <v>-0.473517</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>44985</v>
       </c>
       <c r="B19" t="n">
-        <v>2.956329</v>
+        <v>2.970821</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>45016</v>
       </c>
       <c r="B20" t="n">
-        <v>0.08132200000000001</v>
+        <v>0.001766</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45046</v>
       </c>
       <c r="B21" t="n">
-        <v>1.037108</v>
+        <v>0.848618</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45077</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.726531</v>
+        <v>-1.496142</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45107</v>
       </c>
       <c r="B23" t="n">
-        <v>0.136874</v>
+        <v>0.034305</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45138</v>
       </c>
       <c r="B24" t="n">
-        <v>0.321216</v>
+        <v>0.448214</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45169</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.370842</v>
+        <v>-0.399402</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45199</v>
       </c>
       <c r="B26" t="n">
-        <v>0.123599</v>
+        <v>0.013953</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45230</v>
       </c>
       <c r="B27" t="n">
-        <v>0.290723</v>
+        <v>0.32009</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45260</v>
       </c>
       <c r="B28" t="n">
-        <v>0.632726</v>
+        <v>0.7367669999999999</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>1.324376</v>
+        <v>1.249788</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45322</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.349526</v>
+        <v>-0.387795</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45351</v>
       </c>
       <c r="B31" t="n">
-        <v>0.217311</v>
+        <v>0.188579</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45382</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.047642</v>
+        <v>0.014216</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45412</v>
       </c>
       <c r="B33" t="n">
-        <v>0.045001</v>
+        <v>-0.012122</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45443</v>
       </c>
       <c r="B34" t="n">
-        <v>0.907072</v>
+        <v>0.837831</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45473</v>
       </c>
       <c r="B35" t="n">
-        <v>0.822263</v>
+        <v>1.04753</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45504</v>
       </c>
       <c r="B36" t="n">
-        <v>0.29212</v>
+        <v>0.338409</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45535</v>
       </c>
       <c r="B37" t="n">
-        <v>0.239878</v>
+        <v>0.138518</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45565</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7981780000000001</v>
+        <v>0.799855</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45596</v>
       </c>
       <c r="B39" t="n">
-        <v>0.142964</v>
+        <v>0.193086</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45626</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.155954</v>
+        <v>-0.219287</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45657</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.500274</v>
+        <v>-0.577052</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>0.581806</v>
+        <v>0.67971</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45716</v>
       </c>
       <c r="B43" t="n">
-        <v>0.651126</v>
+        <v>0.500869</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45747</v>
       </c>
       <c r="B44" t="n">
-        <v>1.210865</v>
+        <v>1.302545</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45777</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.333662</v>
+        <v>-0.416951</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45808</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.658621</v>
+        <v>-0.725787</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45838</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.214439</v>
+        <v>0.089546</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45869</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.456297</v>
+        <v>-0.460691</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45900</v>
       </c>
       <c r="B49" t="n">
-        <v>0.489219</v>
+        <v>0.368026</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45930</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.150542</v>
+        <v>-0.07171</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45961</v>
       </c>
       <c r="B51" t="n">
-        <v>0.073161</v>
+        <v>0.011718</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>45991</v>
       </c>
       <c r="B52" t="n">
-        <v>0.513402</v>
+        <v>0.467077</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>46022</v>
       </c>
       <c r="B53" t="n">
-        <v>0.131385</v>
+        <v>0.201306</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46053</v>
       </c>
       <c r="B54" t="n">
-        <v>0.582392</v>
+        <v>0.562015</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46081</v>
       </c>
       <c r="B55" t="n">
-        <v>0.548872</v>
+        <v>0.635194</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46112</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.133871</v>
+        <v>-0.151802</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46142</v>
       </c>
       <c r="B57" t="n">
-        <v>0.404069</v>
+        <v>0.26509</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,15 @@
         <v>46173</v>
       </c>
       <c r="B58" t="n">
-        <v>0.07079299999999999</v>
+        <v>0.027195</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.6395690000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,465 +434,457 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.064886</v>
+        <v>0.541272</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>0.541272</v>
+        <v>1.615792</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>1.615792</v>
+        <v>0.317648</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>0.317648</v>
+        <v>-1.96241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.96241</v>
+        <v>1.093519</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>1.093519</v>
+        <v>1.076776</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>1.076776</v>
+        <v>-0.09649099999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.09649099999999999</v>
+        <v>0.206371</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>0.206371</v>
+        <v>-0.122134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.122134</v>
+        <v>1.910705</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>1.910705</v>
+        <v>-0.328948</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.328948</v>
+        <v>0.052651</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>0.052651</v>
+        <v>0.275674</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>0.275674</v>
+        <v>-0.709488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.709488</v>
+        <v>-0.124753</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.124753</v>
+        <v>-0.473517</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.473517</v>
+        <v>2.970821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>2.970821</v>
+        <v>0.001766</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001766</v>
+        <v>0.848618</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>0.848618</v>
+        <v>-1.496142</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.496142</v>
+        <v>0.034305</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>0.034305</v>
+        <v>0.448214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>0.448214</v>
+        <v>-0.399402</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.399402</v>
+        <v>0.013953</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>0.013953</v>
+        <v>0.32009</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>0.32009</v>
+        <v>0.7367669999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7367669999999999</v>
+        <v>1.249788</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>1.249788</v>
+        <v>-0.387795</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.387795</v>
+        <v>0.188579</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>0.188579</v>
+        <v>0.014216</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>0.014216</v>
+        <v>-0.012122</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.012122</v>
+        <v>0.837831</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>0.837831</v>
+        <v>1.04753</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>1.04753</v>
+        <v>0.338409</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>0.338409</v>
+        <v>0.138518</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>0.138518</v>
+        <v>0.799855</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>0.799855</v>
+        <v>0.193086</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>0.193086</v>
+        <v>-0.219287</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.219287</v>
+        <v>-0.577052</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.577052</v>
+        <v>0.67971</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>0.67971</v>
+        <v>0.500869</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>0.500869</v>
+        <v>1.302545</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>1.302545</v>
+        <v>-0.416951</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.416951</v>
+        <v>-0.725787</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.725787</v>
+        <v>0.089546</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>0.089546</v>
+        <v>-0.460691</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.460691</v>
+        <v>0.368026</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>0.368026</v>
+        <v>-0.07171</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.07171</v>
+        <v>0.011718</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>0.011718</v>
+        <v>0.467077</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>0.467077</v>
+        <v>0.201306</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>0.201306</v>
+        <v>0.562015</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>0.562015</v>
+        <v>0.635194</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>0.635194</v>
+        <v>-0.151802</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.151802</v>
+        <v>0.26509</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>0.26509</v>
+        <v>0.027195</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>0.027195</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B59" t="n">
         <v>-0.6395690000000001</v>
       </c>
     </row>
